--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484867_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484867_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1739</v>
+        <v>4.9154</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4934</v>
+        <v>4.1696</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6806</v>
+        <v>0.7458</v>
       </c>
       <c r="G2" t="n">
         <v>2.8353</v>
@@ -610,13 +610,13 @@
         <v>0.7548</v>
       </c>
       <c r="S2" t="n">
-        <v>5.0179</v>
+        <v>2.7594</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6628</v>
+        <v>1.339</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3551</v>
+        <v>1.4203</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3018</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6855</v>
+        <v>3.9338</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7602</v>
+        <v>1.273</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9254</v>
+        <v>2.6608</v>
       </c>
       <c r="G3" t="n">
         <v>5.5025</v>
@@ -688,13 +688,13 @@
         <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8623</v>
+        <v>1.1106</v>
       </c>
       <c r="T3" t="n">
-        <v>0.77</v>
+        <v>0.2829</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0923</v>
+        <v>0.8277</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6036</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3431</v>
+        <v>2.1385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4549</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8882</v>
+        <v>2.0734</v>
       </c>
       <c r="G4" t="n">
         <v>1.8591</v>
@@ -766,13 +766,13 @@
         <v>0.3774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1952</v>
+        <v>-0.3997</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0559</v>
+        <v>-0.4456</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1393</v>
+        <v>0.0459</v>
       </c>
       <c r="V4" t="n">
         <v>1.2452</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3303</v>
+        <v>1.3338</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2314</v>
+        <v>0.0762</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0989</v>
+        <v>1.2575</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1217</v>
+        <v>0.488</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6301</v>
+        <v>-1.7029</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4916</v>
+        <v>2.1909</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1697</v>
+        <v>-0.5752</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0463</v>
+        <v>-0.839</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1234</v>
+        <v>0.2638</v>
       </c>
       <c r="M5" t="n">
-        <v>0.952</v>
+        <v>1.0632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5838</v>
+        <v>-0.8639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3682</v>
+        <v>1.9271</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0764</v>
+        <v>0.2987</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0617</v>
+        <v>-0.254</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0147</v>
+        <v>0.5527</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2452</v>
+        <v>-0.019</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.9054</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2452</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8676</v>
+        <v>1.2795</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5486</v>
+        <v>1.1541</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4163</v>
+        <v>0.1254</v>
       </c>
       <c r="G6" t="n">
-        <v>0.488</v>
+        <v>2.1217</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7029</v>
+        <v>1.6301</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1909</v>
+        <v>0.4916</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5752</v>
+        <v>1.1697</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.839</v>
+        <v>1.0463</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2638</v>
+        <v>0.1234</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0632</v>
+        <v>0.952</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8639</v>
+        <v>0.5838</v>
       </c>
       <c r="O6" t="n">
-        <v>1.9271</v>
+        <v>0.3682</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1675</v>
+        <v>0.0256</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8789</v>
+        <v>-0.0156</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7114</v>
+        <v>0.0412</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.019</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9244</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3737</v>
+        <v>0.2878</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1512</v>
+        <v>-2.0341</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7775</v>
+        <v>2.322</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9113</v>
+        <v>-1.9859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7466</v>
+        <v>-5.0055</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1647</v>
+        <v>3.0195</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7231</v>
+        <v>-2.2039</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0565</v>
+        <v>-3.0365</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6666</v>
+        <v>0.8326</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1882</v>
+        <v>0.218</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3099</v>
+        <v>-1.969</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4981</v>
+        <v>2.1869</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3492</v>
+        <v>1.2173</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.0568</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3621</v>
+        <v>1.1605</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8868</v>
+        <v>1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.2832</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.93</v>
+        <v>0.1305</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1462</v>
+        <v>0.7228</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2162</v>
+        <v>-0.5923</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9859</v>
+        <v>1.9113</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.0055</v>
+        <v>0.7466</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0195</v>
+        <v>1.1647</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2039</v>
+        <v>1.7231</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.0365</v>
+        <v>1.0565</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8326</v>
+        <v>0.6666</v>
       </c>
       <c r="M9" t="n">
-        <v>0.218</v>
+        <v>0.1882</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.969</v>
+        <v>-0.3099</v>
       </c>
       <c r="O9" t="n">
-        <v>2.1869</v>
+        <v>0.4981</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0553</v>
+        <v>0.2829</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0547</v>
+        <v>-0.1769</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2452</v>
+        <v>-1.8868</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>-1.2832</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.584</v>
+        <v>-0.5056</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2202</v>
+        <v>-0.4592</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3639</v>
+        <v>-0.0464</v>
       </c>
       <c r="G10" t="n">
         <v>0.7548</v>
@@ -1234,13 +1234,13 @@
         <v>0.7548</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3762</v>
+        <v>0.7022</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.0592</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4439</v>
+        <v>0.7613</v>
       </c>
       <c r="V10" t="n">
         <v>0.3018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7645</v>
+        <v>-1.7464</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2529</v>
+        <v>-1.1555</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5909</v>
       </c>
       <c r="G11" t="n">
         <v>2.9374</v>
@@ -1312,13 +1312,13 @@
         <v>0.3774</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3621</v>
+        <v>-0.344</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4703</v>
+        <v>-0.3729</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1082</v>
+        <v>0.0289</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8868</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.1295</v>
+        <v>12.4012</v>
       </c>
       <c r="E12" t="n">
-        <v>4.557100000000002</v>
+        <v>4.445899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>8.572600000000001</v>
+        <v>7.955299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>17.0581</v>
@@ -1390,22 +1390,22 @@
         <v>5.0949</v>
       </c>
       <c r="S12" t="n">
-        <v>6.2042</v>
+        <v>5.476100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9251999999999998</v>
+        <v>0.8143</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2789</v>
+        <v>4.6616</v>
       </c>
       <c r="V12" t="n">
         <v>-3.151</v>
       </c>
       <c r="W12" t="n">
-        <v>3.942400000000001</v>
+        <v>3.9424</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.0934</v>
+        <v>-7.093400000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4502</v>
+        <v>4.5018</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4441</v>
+        <v>5.1518</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9939</v>
+        <v>-0.65</v>
       </c>
       <c r="G13" t="n">
         <v>2.3043</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0053</v>
+        <v>-0.9537</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4986</v>
+        <v>-0.7909</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.1627</v>
       </c>
       <c r="V13" t="n">
         <v>1.2642</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5676</v>
+        <v>2.3992</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9843</v>
+        <v>0.7894</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5833</v>
+        <v>1.6097</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1991</v>
@@ -1546,13 +1546,13 @@
         <v>1.887</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3279</v>
+        <v>-1.4963</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8789</v>
+        <v>-1.0738</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.449</v>
+        <v>-0.4226</v>
       </c>
       <c r="V14" t="n">
         <v>2.2076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8364</v>
+        <v>-0.9855</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0164</v>
+        <v>-0.3603</v>
       </c>
       <c r="G15" t="n">
         <v>-2.3938</v>
@@ -1624,13 +1624,13 @@
         <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1235</v>
+        <v>-0.0256</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2664</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3898</v>
+        <v>0.0459</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.285</v>
+        <v>-1.7535</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.3684</v>
+        <v>-1.8733</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0834</v>
+        <v>0.1198</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.5178</v>
+        <v>-2.3591</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5027</v>
+        <v>1.1199</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.0206</v>
+        <v>-3.479</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2285</v>
+        <v>-1.6713</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2773</v>
+        <v>0.8773</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.5058</v>
+        <v>-2.5486</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2893</v>
+        <v>-0.6878</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2254</v>
+        <v>0.2426</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5148</v>
+        <v>-0.9304</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.616</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1017</v>
+        <v>-1.1264</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4857</v>
+        <v>0.5432</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8488</v>
+        <v>-0.3208</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8488</v>
+        <v>0.9244</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GOMEZ VELEZ</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2999</v>
+        <v>-1.9766</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4313</v>
+        <v>-2.3063</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8686</v>
+        <v>0.3298</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7023</v>
+        <v>-3.454</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0728</v>
+        <v>-1.1136</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7751</v>
+        <v>-2.3404</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1526</v>
+        <v>-2.4515</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4969</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6496</v>
+        <v>-1.9076</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5497</v>
+        <v>-1.0026</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4241</v>
+        <v>-0.5697</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1256</v>
+        <v>-0.4329</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9941</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2787</v>
+        <v>0.1451</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7154</v>
+        <v>-0.064</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9244</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9244</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>S. GOMEZ VELEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3019</v>
+        <v>-2.2038</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2631</v>
+        <v>-0.6262</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0389</v>
+        <v>-1.5776</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3591</v>
+        <v>-1.7023</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1199</v>
+        <v>0.0728</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.479</v>
+        <v>-1.7751</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6713</v>
+        <v>-0.1526</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8773</v>
+        <v>0.4969</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.5486</v>
+        <v>-0.6496</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6878</v>
+        <v>-1.5497</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2426</v>
+        <v>-0.4241</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9304</v>
+        <v>-1.1256</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1316</v>
+        <v>-0.898</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5161</v>
+        <v>-0.4736</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3845</v>
+        <v>-0.4244</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3208</v>
+        <v>-0.9244</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2452</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MARTINEZ BERTOMEU</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3942</v>
+        <v>-2.7083</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7537</v>
+        <v>-3.3684</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6404</v>
+        <v>0.6601</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.262</v>
+        <v>-3.5178</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.329</v>
+        <v>2.5027</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9329</v>
+        <v>-6.0206</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4584</v>
+        <v>-2.2285</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4995</v>
+        <v>2.2773</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0411</v>
+        <v>-4.5058</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8036</v>
+        <v>-1.2893</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8295</v>
+        <v>0.2254</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9741</v>
+        <v>-1.5148</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6225000000000001</v>
+        <v>-1.0393</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7236</v>
+        <v>-1.1017</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1011</v>
+        <v>0.0624</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3208</v>
+        <v>1.8488</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.019</v>
+        <v>1.8488</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>R. MARTINEZ BERTOMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9941</v>
+        <v>-2.7407</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0858</v>
+        <v>-1.3384</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0917</v>
+        <v>-1.4023</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.454</v>
+        <v>-3.262</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1136</v>
+        <v>-2.329</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3404</v>
+        <v>-0.9329</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4515</v>
+        <v>-1.4584</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-1.4995</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9076</v>
+        <v>0.0411</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0026</v>
+        <v>-1.8036</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5697</v>
+        <v>-0.8295</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4329</v>
+        <v>-0.9741</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9365</v>
+        <v>0.276</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6343</v>
+        <v>0.139</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3021</v>
+        <v>0.137</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0595</v>
+        <v>-6.686</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1889</v>
+        <v>-4.2863</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8707</v>
+        <v>-2.3997</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3752</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3157</v>
+        <v>-0.3108</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.749</v>
+        <v>-0.8464</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0647</v>
+        <v>0.5356</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4904</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.1532</v>
+        <v>-12.1534</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.482900000000001</v>
+        <v>-8.482899999999999</v>
       </c>
       <c r="F22" t="n">
         <v>-3.6705</v>
@@ -2137,7 +2137,7 @@
         <v>-16.959</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1478</v>
+        <v>4.147799999999999</v>
       </c>
       <c r="I22" t="n">
         <v>-21.1067</v>
@@ -2146,7 +2146,7 @@
         <v>-4.715199999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>6.7613</v>
+        <v>6.761299999999999</v>
       </c>
       <c r="L22" t="n">
         <v>-11.4766</v>
@@ -2170,16 +2170,16 @@
         <v>12.2655</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.949700000000001</v>
+        <v>-4.949800000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.200099999999999</v>
+        <v>-5.2002</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2504999999999999</v>
+        <v>0.2504000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>3.151</v>
+        <v>3.151000000000001</v>
       </c>
       <c r="W22" t="n">
         <v>7.093400000000001</v>
